--- a/data/trans_orig/P32E$bar_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023</t>
+          <t>Población según los lugares donde se realiza el consumo de alcohol (atracón) (multirrespuesta) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30715</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39247</t>
+          <t>38705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>17289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16747</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>15985</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44331</t>
+          <t>43634</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22905</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>34166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21554</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -1751,97 +1751,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2963</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8792</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>40,71%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2963</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8673</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>11064</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>40,16%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2963</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>11111</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>20461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -2320,97 +2320,97 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1690</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3863</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>81,25%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>1045</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>4311</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>5459</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>90,66%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>4966</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45785</t>
+          <t>46049</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40843</t>
+          <t>41813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57129</t>
+          <t>57125</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37210</t>
+          <t>37502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43740</t>
+          <t>44473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>20266</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>18698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,62 +2924,62 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6545</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>8240</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>82776</t>
+          <t>83638</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>106876</t>
+          <t>108288</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45948</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122822</t>
+          <t>122849</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149033</t>
+          <t>150025</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87186</t>
+          <t>87956</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78322</t>
+          <t>79562</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107576</t>
+          <t>109730</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23355</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>46973</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>58588</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>40750</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>25652</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>51410</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32E$bar_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32E$bar_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27182</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30807</t>
+          <t>31799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34199</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38705</t>
+          <t>40187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18881</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>22060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21178</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>29185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>22234</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>45106</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>35626</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43634</t>
+          <t>52023</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>29967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>34439</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>43712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23419</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>14093</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22209</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,27 +1898,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8632</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20139</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,27 +2011,27 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39960</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32701</t>
+          <t>34022</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46049</t>
+          <t>48292</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>50071</t>
+          <t>54175</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41813</t>
+          <t>44384</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57125</t>
+          <t>61975</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>31917</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21357</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37502</t>
+          <t>40553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34666</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26209</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44473</t>
+          <t>48186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>60,87%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>21505</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>739</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>26617</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83638</t>
+          <t>91893</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108288</t>
+          <t>117638</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>37657</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>152399</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122849</t>
+          <t>137276</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>150025</t>
+          <t>166546</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>87085</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62476</t>
+          <t>72468</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87956</t>
+          <t>100652</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>109790</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79562</t>
+          <t>92920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109730</t>
+          <t>126553</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>53549</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32587</t>
+          <t>39074</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58588</t>
+          <t>70110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>40750</t>
+          <t>41745</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38264</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>27593</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>53671</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
